--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
@@ -30,12 +30,6 @@
     <t>Kích thước</t>
   </si>
   <si>
-    <t>Khung 1</t>
-  </si>
-  <si>
-    <t>Khung 2</t>
-  </si>
-  <si>
     <t>Pcs/SH</t>
   </si>
   <si>
@@ -79,6 +73,12 @@
   </si>
   <si>
     <t>Lớp 4</t>
+  </si>
+  <si>
+    <t>Line 1</t>
+  </si>
+  <si>
+    <t>Line 2</t>
   </si>
 </sst>
 </file>
@@ -466,55 +466,55 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -30,12 +30,6 @@
     <t>Kích thước</t>
   </si>
   <si>
-    <t>Pcs/SH</t>
-  </si>
-  <si>
-    <t>Block/SH</t>
-  </si>
-  <si>
     <t>Số lớp</t>
   </si>
   <si>
@@ -60,9 +54,6 @@
     <t>Tape dùng chung</t>
   </si>
   <si>
-    <t>Loại TAPE</t>
-  </si>
-  <si>
     <t>Lớp 1</t>
   </si>
   <si>
@@ -75,10 +66,16 @@
     <t>Lớp 4</t>
   </si>
   <si>
-    <t>Line 1</t>
-  </si>
-  <si>
-    <t>Line 2</t>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Khung</t>
+  </si>
+  <si>
+    <t>Pcs/Block</t>
+  </si>
+  <si>
+    <t>Block</t>
   </si>
 </sst>
 </file>
@@ -430,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
@@ -447,15 +444,14 @@
     <col min="12" max="13" width="15" style="1" customWidth="1"/>
     <col min="14" max="14" width="16" style="1" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="11.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -466,55 +462,52 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
@@ -39,9 +39,6 @@
     <t>S.R/No S.R</t>
   </si>
   <si>
-    <t>Chủng hàng</t>
-  </si>
-  <si>
     <t>RING/JIG</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>Block</t>
+  </si>
+  <si>
+    <t>Tên nguyên vật liệu</t>
   </si>
 </sst>
 </file>
@@ -462,52 +462,52 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>S.R/No S.R</t>
-  </si>
-  <si>
-    <t>RING/JIG</t>
   </si>
   <si>
     <t>Process</t>
@@ -427,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
@@ -441,17 +438,17 @@
     <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="15" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -462,25 +459,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>3</v>
@@ -505,9 +502,6 @@
       </c>
       <c r="R1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
